--- a/hexaly_benchmarking_results/original.xlsx
+++ b/hexaly_benchmarking_results/original.xlsx
@@ -490,10 +490,10 @@
         <v>-451</v>
       </c>
       <c r="C5">
-        <v>-451.0000000000001</v>
+        <v>-451.0000015212911</v>
       </c>
       <c r="D5">
-        <v>1.260386227512373E-14</v>
+        <v>3.373150978979085E-07</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -510,10 +510,10 @@
         <v>-659.0000000000011</v>
       </c>
       <c r="C6">
-        <v>-659.0000029995625</v>
+        <v>-659.0000058793472</v>
       </c>
       <c r="D6">
-        <v>4.551686456680926E-07</v>
+        <v>8.921617639150925E-07</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-868.0000000000008</v>
+        <v>-868.0000024296039</v>
       </c>
       <c r="C7">
-        <v>-868.0000125144657</v>
+        <v>-868.0000104394529</v>
       </c>
       <c r="D7">
-        <v>1.441758603221917E-06</v>
+        <v>9.227936538340633E-07</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -547,16 +547,16 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1060.500006047846</v>
+        <v>-1060.500000000003</v>
       </c>
       <c r="C8">
-        <v>-1060.500006047846</v>
+        <v>-1060.500008584523</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>8.09478622013932E-07</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -567,10 +567,10 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-1254.000010909923</v>
+        <v>-1254.00001208822</v>
       </c>
       <c r="C9">
-        <v>-1254.000010909923</v>
+        <v>-1254.00001208822</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-1449.000002314006</v>
+        <v>-1449.000013392257</v>
       </c>
       <c r="C10">
-        <v>-1449.00001634352</v>
+        <v>-1449.000013392257</v>
       </c>
       <c r="D10">
-        <v>9.68220415388498E-07</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -607,10 +607,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-1635.00001451674</v>
+        <v>-1635.000130841272</v>
       </c>
       <c r="C11">
-        <v>-1635.00001451674</v>
+        <v>-1635.000130841272</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -627,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-2002.000072418226</v>
+        <v>-2002.000062460383</v>
       </c>
       <c r="C12">
-        <v>-2025.725864457231</v>
+        <v>-2025.971366660958</v>
       </c>
       <c r="D12">
-        <v>1.171224224130721</v>
+        <v>1.183200542467784</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -647,16 +647,16 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-2218.000044036527</v>
+        <v>-2218.00003108264</v>
       </c>
       <c r="C13">
-        <v>-2218.000044036527</v>
+        <v>-2218.00003152675</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2.002298893336025E-08</v>
       </c>
       <c r="E13">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -667,13 +667,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-2587.000073984655</v>
+        <v>-2587.000117654644</v>
       </c>
       <c r="C14">
-        <v>-2611.888474705629</v>
+        <v>-2611.832189873512</v>
       </c>
       <c r="D14">
-        <v>0.9528891054117093</v>
+        <v>0.9507529739140849</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -687,13 +687,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-2914.999790373957</v>
+        <v>-2909.194650371329</v>
       </c>
       <c r="C15">
         <v>-12324.00000000002</v>
       </c>
       <c r="D15">
-        <v>76.34696697197377</v>
+        <v>76.39407132123235</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -707,13 +707,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-3458.500264370593</v>
+        <v>-3458.500264687492</v>
       </c>
       <c r="C16">
         <v>-14952.00000000003</v>
       </c>
       <c r="D16">
-        <v>76.86931337365847</v>
+        <v>76.86931337153902</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -727,13 +727,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-4201.000136032137</v>
+        <v>-4206.499657912642</v>
       </c>
       <c r="C17">
         <v>-18456.00000000004</v>
       </c>
       <c r="D17">
-        <v>77.23775392266944</v>
+        <v>77.20795590641183</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -747,13 +747,13 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>-4762.585427314091</v>
+        <v>-4691.000129852877</v>
       </c>
       <c r="C18">
         <v>-20524.00000000002</v>
       </c>
       <c r="D18">
-        <v>76.79504274354861</v>
+        <v>77.14383097908365</v>
       </c>
       <c r="E18">
         <v>300</v>
@@ -767,13 +767,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-6164.0003739276</v>
+        <v>-6186.99978637411</v>
       </c>
       <c r="C19">
         <v>-22084.00000000004</v>
       </c>
       <c r="D19">
-        <v>72.08838809125344</v>
+        <v>71.98424295248098</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -787,13 +787,13 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>-7685.000519772417</v>
+        <v>-7749.495693290531</v>
       </c>
       <c r="C20">
         <v>-25108.00000000009</v>
       </c>
       <c r="D20">
-        <v>69.39222351532423</v>
+        <v>69.13535250402062</v>
       </c>
       <c r="E20">
         <v>300</v>
@@ -807,13 +807,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-12950.0005945792</v>
+        <v>-12950.00061152834</v>
       </c>
       <c r="C21">
         <v>-28000</v>
       </c>
       <c r="D21">
-        <v>53.74999787650285</v>
+        <v>53.74999781597022</v>
       </c>
       <c r="E21">
         <v>300</v>
@@ -897,16 +897,16 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>-145.000009719712</v>
+        <v>-145.000010023737</v>
       </c>
       <c r="C4">
-        <v>-145.000009719712</v>
+        <v>-145.000010023737</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -917,16 +917,16 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-451.0000184371061</v>
+        <v>-451.0000206246843</v>
       </c>
       <c r="C5">
-        <v>-451.0000184371061</v>
+        <v>-451.0000206246843</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -937,13 +937,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-565.0000161680553</v>
+        <v>-565.0000159276717</v>
       </c>
       <c r="C6">
         <v>-1771.731492813431</v>
       </c>
       <c r="D6">
-        <v>68.11029106499313</v>
+        <v>68.11029107856085</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -957,13 +957,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-728.0000131643623</v>
+        <v>-728.0000202896014</v>
       </c>
       <c r="C7">
         <v>-3426.505201707036</v>
       </c>
       <c r="D7">
-        <v>78.75386230840439</v>
+        <v>78.75386210045961</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -977,13 +977,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-660.0000116664627</v>
+        <v>-660.0000183779347</v>
       </c>
       <c r="C8">
         <v>-5404.117354618282</v>
       </c>
       <c r="D8">
-        <v>87.78708957712705</v>
+        <v>87.78708945293521</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -997,13 +997,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-703.7599275211328</v>
+        <v>-698.4933507422611</v>
       </c>
       <c r="C9">
         <v>-6136.465232134065</v>
       </c>
       <c r="D9">
-        <v>88.5315095759715</v>
+        <v>88.61733385069066</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1017,13 +1017,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-742.7499878421355</v>
+        <v>-742.7498734940593</v>
       </c>
       <c r="C10">
         <v>-7391.707267549545</v>
       </c>
       <c r="D10">
-        <v>89.9515773425864</v>
+        <v>89.95157888956429</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1077,13 +1077,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-1108.000044914146</v>
+        <v>-1108.000047195343</v>
       </c>
       <c r="C13">
         <v>-10770.96185463446</v>
       </c>
       <c r="D13">
-        <v>89.71308171110638</v>
+        <v>89.71308168992725</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1287,19 +1287,19 @@
         <v>120</v>
       </c>
       <c r="B2">
-        <v>-1.194235812151874E-05</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-60.00000000000001</v>
+        <v>-0</v>
       </c>
       <c r="D2">
-        <v>99.99998009606979</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1307,13 +1307,13 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>-2.396254058390355E-05</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>-203.9998545237506</v>
       </c>
       <c r="D3">
-        <v>99.9999882536482</v>
+        <v>100</v>
       </c>
       <c r="E3">
         <v>300</v>
@@ -1327,13 +1327,13 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>-3.597395246298447E-05</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>-503.999785307129</v>
+        <v>-504.0004291743462</v>
       </c>
       <c r="D4">
-        <v>99.99999286230799</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -1347,13 +1347,13 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-4.797766349020306E-05</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>-924.0001431768294</v>
+        <v>-924.0004824820539</v>
       </c>
       <c r="D5">
-        <v>99.99999480761298</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -1367,13 +1367,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-5.996395570330527E-05</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>-1464.000481230503</v>
+        <v>-1464.002281996201</v>
       </c>
       <c r="D6">
-        <v>99.99999590410273</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -1387,13 +1387,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-7.19294551852553E-05</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>-2124.002688624019</v>
       </c>
       <c r="D7">
-        <v>99.99999661349509</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -1407,13 +1407,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-8.394699368185837E-05</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>-2903.998466110931</v>
       </c>
       <c r="D8">
-        <v>99.99999710926178</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1427,13 +1427,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-9.586974905358557E-05</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>-3803.999294738233</v>
       </c>
       <c r="D9">
-        <v>99.99999747976427</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1447,13 +1447,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-0.0001079084193871224</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>-4823.995644388162</v>
       </c>
       <c r="D10">
-        <v>99.99999776309045</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1467,13 +1467,13 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-0.0001198580890553851</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>-5964.000269188775</v>
       </c>
       <c r="D11">
-        <v>99.99999799030711</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -1487,13 +1487,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-0.0001438274181703434</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>-8603.994038989475</v>
       </c>
       <c r="D12">
-        <v>99.99999832836451</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -1507,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-0.0001558061960154773</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>-10103.9940737759</v>
       </c>
       <c r="D13">
-        <v>99.99999845797419</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1527,13 +1527,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-0.0001797476715503646</v>
+        <v>-3</v>
       </c>
       <c r="C14">
         <v>-13464.00702788861</v>
       </c>
       <c r="D14">
-        <v>99.9999986649764</v>
+        <v>99.97771837170178</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -1547,13 +1547,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-0.0002023040726352716</v>
+        <v>-3</v>
       </c>
       <c r="C15">
         <v>-17304.03247502964</v>
       </c>
       <c r="D15">
-        <v>99.99999883088481</v>
+        <v>99.98266300063682</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -1567,13 +1567,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-0.00023611705610727</v>
+        <v>-14</v>
       </c>
       <c r="C16">
         <v>-23963.98555582502</v>
       </c>
       <c r="D16">
-        <v>99.99999901470039</v>
+        <v>99.94157900000654</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -1587,13 +1587,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-0.0002722242112440137</v>
+        <v>-14</v>
       </c>
       <c r="C17">
-        <v>-28000</v>
+        <v>-27975.02526999412</v>
       </c>
       <c r="D17">
-        <v>99.99999902777068</v>
+        <v>99.94995536245318</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -1607,13 +1607,13 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>-0.0002172152973278617</v>
+        <v>-17</v>
       </c>
       <c r="C18">
-        <v>-28000</v>
+        <v>-27975.02526999412</v>
       </c>
       <c r="D18">
-        <v>99.99999922423109</v>
+        <v>99.93923151155029</v>
       </c>
       <c r="E18">
         <v>300</v>
@@ -1627,13 +1627,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-0.0001815481506075266</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-28000</v>
+        <v>-27979.9818255575</v>
       </c>
       <c r="D19">
-        <v>99.99999935161374</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -1647,13 +1647,13 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>-0.0001388466923757919</v>
+        <v>-28</v>
       </c>
       <c r="C20">
-        <v>-28000</v>
+        <v>-27979.9818255575</v>
       </c>
       <c r="D20">
-        <v>99.99999950411896</v>
+        <v>99.8999284553701</v>
       </c>
       <c r="E20">
         <v>300</v>
@@ -1667,13 +1667,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-0.0001174684875643222</v>
+        <v>-28</v>
       </c>
       <c r="C21">
-        <v>-28000</v>
+        <v>-27979.9818255575</v>
       </c>
       <c r="D21">
-        <v>99.99999958046969</v>
+        <v>99.8999284553701</v>
       </c>
       <c r="E21">
         <v>300</v>
@@ -1737,13 +1737,13 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>-86</v>
+        <v>-86.00000000000003</v>
       </c>
       <c r="C3">
         <v>-86.00000000000003</v>
       </c>
       <c r="D3">
-        <v>3.304849933767907E-14</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1757,13 +1757,13 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>-145.0000035864396</v>
+        <v>-145.0000000000001</v>
       </c>
       <c r="C4">
-        <v>-145.0000035864396</v>
+        <v>-145.0000000000001</v>
       </c>
       <c r="D4">
-        <v>3.920235686540631E-14</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1777,16 +1777,16 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-451.0000353377108</v>
+        <v>-451.0000343272736</v>
       </c>
       <c r="C5">
-        <v>-451.0000353377108</v>
+        <v>-451.0000343272736</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -1797,16 +1797,16 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-659.0000303256452</v>
+        <v>-659.0000237442974</v>
       </c>
       <c r="C6">
-        <v>-659.0000303256452</v>
+        <v>-659.0000251974584</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2.205100010114148E-07</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -1817,16 +1817,16 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-868.0000603696883</v>
+        <v>-868.0000571720884</v>
       </c>
       <c r="C7">
-        <v>-868.0000603696883</v>
+        <v>-868.0000571720884</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -1837,13 +1837,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1060.500061494765</v>
+        <v>-1060.50006049484</v>
       </c>
       <c r="C8">
-        <v>-1781.197769260061</v>
+        <v>-1772.544375686975</v>
       </c>
       <c r="D8">
-        <v>40.46140862082292</v>
+        <v>40.17074691944862</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1857,13 +1857,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-1254.000075557921</v>
+        <v>-1254.000081548945</v>
       </c>
       <c r="C9">
         <v>-2363.082998326638</v>
       </c>
       <c r="D9">
-        <v>46.93372698098576</v>
+        <v>46.93372672746003</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1877,13 +1877,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-1449.000094548453</v>
+        <v>-1449.000091779117</v>
       </c>
       <c r="C10">
         <v>-2845.549047076071</v>
       </c>
       <c r="D10">
-        <v>49.07836517394189</v>
+        <v>49.07836527126356</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1897,13 +1897,13 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-1635.000171036218</v>
+        <v>-1635.000163509643</v>
       </c>
       <c r="C11">
         <v>-3318.756098918216</v>
       </c>
       <c r="D11">
-        <v>50.73454865908452</v>
+        <v>50.73454888587358</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -1917,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-1979.000139158466</v>
+        <v>-1997.625110585045</v>
       </c>
       <c r="C12">
         <v>-4244.750460012079</v>
       </c>
       <c r="D12">
-        <v>53.37770364119745</v>
+        <v>52.93892704874433</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -1937,13 +1937,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-2172.000107177197</v>
+        <v>-2173.000155713786</v>
       </c>
       <c r="C13">
         <v>-4732.462068965503</v>
       </c>
       <c r="D13">
-        <v>54.10422575976425</v>
+        <v>54.08309408407377</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1957,13 +1957,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-2500.000140018817</v>
+        <v>-2538.500231431382</v>
       </c>
       <c r="C14">
         <v>-5944.883997635979</v>
       </c>
       <c r="D14">
-        <v>57.94703242295463</v>
+        <v>57.29941522087171</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -1977,13 +1977,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-2745.875195881951</v>
+        <v>-2918.000230485854</v>
       </c>
       <c r="C15">
         <v>-12072.00941456705</v>
       </c>
       <c r="D15">
-        <v>77.25419935003896</v>
+        <v>75.82838009582099</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-3381.002136630168</v>
+        <v>-0.0002131862964693827</v>
       </c>
       <c r="C16">
         <v>-14700.01230382703</v>
       </c>
       <c r="D16">
-        <v>77.00000471598278</v>
+        <v>99.9999985497543</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -2017,13 +2017,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-4192.502251375493</v>
+        <v>-4169.000319999496</v>
       </c>
       <c r="C17">
         <v>-18203.988754082</v>
       </c>
       <c r="D17">
-        <v>76.96932080099545</v>
+        <v>77.09842399751727</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -2057,13 +2057,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-0.0004529695874760642</v>
+        <v>-0.0004529591657500301</v>
       </c>
       <c r="C19">
         <v>-22054.0168671837</v>
       </c>
       <c r="D19">
-        <v>99.99999794609032</v>
+        <v>99.99999794613758</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -2077,13 +2077,13 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>-0.0006901101309554744</v>
+        <v>-0.0006902246848604343</v>
       </c>
       <c r="C20">
         <v>-25108.00000000009</v>
       </c>
       <c r="D20">
-        <v>99.99999725143329</v>
+        <v>99.99999725097703</v>
       </c>
       <c r="E20">
         <v>300</v>
@@ -2097,13 +2097,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-0.001318997787629534</v>
+        <v>-0.001315768683549798</v>
       </c>
       <c r="C21">
         <v>-28000</v>
       </c>
       <c r="D21">
-        <v>99.99999528929362</v>
+        <v>99.99999530082613</v>
       </c>
       <c r="E21">
         <v>300</v>
@@ -2167,13 +2167,13 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>-21.00000239966293</v>
+        <v>-86.00000000000003</v>
       </c>
       <c r="C3">
         <v>-126.0000885118292</v>
       </c>
       <c r="D3">
-        <v>83.33334313674598</v>
+        <v>31.74607969269313</v>
       </c>
       <c r="E3">
         <v>300</v>
@@ -2187,13 +2187,13 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>-6.000004798896625</v>
+        <v>-145.0000104378069</v>
       </c>
       <c r="C4">
         <v>-281.999926757077</v>
       </c>
       <c r="D4">
-        <v>97.87233817118499</v>
+        <v>48.58154322759305</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -2207,13 +2207,13 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-358.0000286668203</v>
+        <v>-195.0000231381525</v>
       </c>
       <c r="C5">
         <v>-936.0000000000003</v>
       </c>
       <c r="D5">
-        <v>61.75213368944229</v>
+        <v>79.16666419464184</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -2227,13 +2227,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-199.0000215223133</v>
+        <v>-659.0000335999999</v>
       </c>
       <c r="C6">
         <v>-1812.000000000001</v>
       </c>
       <c r="D6">
-        <v>89.01765885638447</v>
+        <v>63.63134472406182</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -2247,13 +2247,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-97.00003340866303</v>
+        <v>-868.0000555389955</v>
       </c>
       <c r="C7">
         <v>-2435.998995109198</v>
       </c>
       <c r="D7">
-        <v>96.01805938329974</v>
+        <v>64.36779911314841</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -2267,13 +2267,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-714.0000587687383</v>
+        <v>-1060.500072872644</v>
       </c>
       <c r="C8">
         <v>-3312.004444742535</v>
       </c>
       <c r="D8">
-        <v>78.4420561421003</v>
+        <v>67.98011323456771</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -2287,13 +2287,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-685.0000723863103</v>
+        <v>-1254.000079633853</v>
       </c>
       <c r="C9">
         <v>-4188.005371744407</v>
       </c>
       <c r="D9">
-        <v>83.64376328149285</v>
+        <v>70.05734309477424</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -2307,13 +2307,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-1134.00007399943</v>
+        <v>-1442.0000948294</v>
       </c>
       <c r="C10">
         <v>-5064.000362915775</v>
       </c>
       <c r="D10">
-        <v>77.60663521464501</v>
+        <v>71.52448673998281</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -2327,13 +2327,13 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-626.0001173430436</v>
+        <v>-1616.000115152116</v>
       </c>
       <c r="C11">
         <v>-5939.994871392595</v>
       </c>
       <c r="D11">
-        <v>89.46126838664622</v>
+        <v>72.79458736681947</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -2347,13 +2347,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-1424.000164321295</v>
+        <v>-1997.000146613521</v>
       </c>
       <c r="C12">
         <v>-7691.994480834661</v>
       </c>
       <c r="D12">
-        <v>81.48724407084109</v>
+        <v>74.03794098410707</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -2367,13 +2367,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-989.0001387471989</v>
+        <v>-2194.500111271641</v>
       </c>
       <c r="C13">
         <v>-8567.994145187473</v>
       </c>
       <c r="D13">
-        <v>88.45703997938996</v>
+        <v>74.38723610117938</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -2387,13 +2387,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-2086.286211443587</v>
+        <v>-2536.500062055725</v>
       </c>
       <c r="C14">
         <v>-10319.99875493886</v>
       </c>
       <c r="D14">
-        <v>79.78404589976186</v>
+        <v>75.42150806130836</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -2407,13 +2407,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-1678.000191880925</v>
+        <v>-2937.500192841713</v>
       </c>
       <c r="C15">
         <v>-12072.00941456705</v>
       </c>
       <c r="D15">
-        <v>86.10007551968842</v>
+        <v>75.6668497185142</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -2427,13 +2427,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-2549.000857212065</v>
+        <v>-3476.437746861758</v>
       </c>
       <c r="C16">
         <v>-14700.01230382703</v>
       </c>
       <c r="D16">
-        <v>82.65987262780418</v>
+        <v>76.35078342106765</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -2447,13 +2447,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-3715.125243563834</v>
+        <v>-4234.437719060752</v>
       </c>
       <c r="C17">
         <v>-18203.988754082</v>
       </c>
       <c r="D17">
-        <v>79.59169666740885</v>
+        <v>76.73895663052836</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -2467,13 +2467,13 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>-3235.002422592539</v>
+        <v>-5014.000299135063</v>
       </c>
       <c r="C18">
-        <v>-20493.99185878009</v>
+        <v>-20524.00000000002</v>
       </c>
       <c r="D18">
-        <v>84.21487407195104</v>
+        <v>75.57006285745928</v>
       </c>
       <c r="E18">
         <v>300</v>
@@ -2487,13 +2487,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-4515.002572573505</v>
+        <v>-6392.000456630823</v>
       </c>
       <c r="C19">
         <v>-22084.00000000004</v>
       </c>
       <c r="D19">
-        <v>79.55532252955308</v>
+        <v>71.05596605401733</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -2507,13 +2507,13 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>-0.0006909135205504337</v>
+        <v>-7878.001293186947</v>
       </c>
       <c r="C20">
         <v>-25108.00000000009</v>
       </c>
       <c r="D20">
-        <v>99.99999724823356</v>
+        <v>68.62354112957257</v>
       </c>
       <c r="E20">
         <v>300</v>
@@ -2527,13 +2527,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-11541.00166371359</v>
+        <v>-0.001396066706475298</v>
       </c>
       <c r="C21">
         <v>-28000</v>
       </c>
       <c r="D21">
-        <v>58.78213691530861</v>
+        <v>99.99999501404749</v>
       </c>
       <c r="E21">
         <v>300</v>

--- a/hexaly_benchmarking_results/original.xlsx
+++ b/hexaly_benchmarking_results/original.xlsx
@@ -490,10 +490,10 @@
         <v>-451</v>
       </c>
       <c r="C5">
-        <v>-451.0000015212911</v>
+        <v>-451.0000000000001</v>
       </c>
       <c r="D5">
-        <v>3.373150978979085E-07</v>
+        <v>1.260386227512373E-14</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -507,13 +507,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-659.0000000000011</v>
+        <v>-659.0000000000049</v>
       </c>
       <c r="C6">
-        <v>-659.0000058793472</v>
+        <v>-659.0000000000147</v>
       </c>
       <c r="D6">
-        <v>8.921617639150925E-07</v>
+        <v>1.483621857975533E-12</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -527,16 +527,16 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-868.0000024296039</v>
+        <v>-868</v>
       </c>
       <c r="C7">
-        <v>-868.0000104394529</v>
+        <v>-868.0000025785014</v>
       </c>
       <c r="D7">
-        <v>9.227936538340633E-07</v>
+        <v>2.970623701328033E-07</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -547,13 +547,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1060.500000000003</v>
+        <v>-1060.5</v>
       </c>
       <c r="C8">
-        <v>-1060.500008584523</v>
+        <v>-1060.500008969101</v>
       </c>
       <c r="D8">
-        <v>8.09478622013932E-07</v>
+        <v>8.457425893436546E-07</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-1254.00001208822</v>
+        <v>-1254.000010673939</v>
       </c>
       <c r="C9">
-        <v>-1254.00001208822</v>
+        <v>-1254.0000135885</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2.324210965414473E-07</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -587,16 +587,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-1449.000013392257</v>
+        <v>-1449.000019407469</v>
       </c>
       <c r="C10">
-        <v>-1449.000013392257</v>
+        <v>-1449.000022261136</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1.969404042430842E-07</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -607,10 +607,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-1635.000130841272</v>
+        <v>-1635.000028695332</v>
       </c>
       <c r="C11">
-        <v>-1635.000130841272</v>
+        <v>-1635.000028695332</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -627,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-2002.000062460383</v>
+        <v>-2002.000069768718</v>
       </c>
       <c r="C12">
-        <v>-2025.971366660958</v>
+        <v>-2022.45127119577</v>
       </c>
       <c r="D12">
-        <v>1.183200542467784</v>
+        <v>1.011208611961311</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -647,16 +647,16 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-2218.00003108264</v>
+        <v>-2218.000044128065</v>
       </c>
       <c r="C13">
-        <v>-2218.00003152675</v>
+        <v>-2218.000044128065</v>
       </c>
       <c r="D13">
-        <v>2.002298893336025E-08</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -667,13 +667,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-2587.000117654644</v>
+        <v>-2587.000071302309</v>
       </c>
       <c r="C14">
-        <v>-2611.832189873512</v>
+        <v>-2609.672447283708</v>
       </c>
       <c r="D14">
-        <v>0.9507529739140849</v>
+        <v>0.8687824406851565</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -687,13 +687,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-2909.194650371329</v>
+        <v>-2930.000077032289</v>
       </c>
       <c r="C15">
         <v>-12324.00000000002</v>
       </c>
       <c r="D15">
-        <v>76.39407132123235</v>
+        <v>76.22525091664812</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -707,13 +707,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-3458.500264687492</v>
+        <v>-3453.000088475215</v>
       </c>
       <c r="C16">
         <v>-14952.00000000003</v>
       </c>
       <c r="D16">
-        <v>76.86931337153902</v>
+        <v>76.90609892673081</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -727,13 +727,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-4206.499657912642</v>
+        <v>-4231.000263853662</v>
       </c>
       <c r="C17">
         <v>-18456.00000000004</v>
       </c>
       <c r="D17">
-        <v>77.20795590641183</v>
+        <v>77.0752044654657</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -747,13 +747,13 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>-4691.000129852877</v>
+        <v>-4754.500101525319</v>
       </c>
       <c r="C18">
         <v>-20524.00000000002</v>
       </c>
       <c r="D18">
-        <v>77.14383097908365</v>
+        <v>76.83443723677006</v>
       </c>
       <c r="E18">
         <v>300</v>
@@ -767,13 +767,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-6186.99978637411</v>
+        <v>-6691.000445128913</v>
       </c>
       <c r="C19">
         <v>-22084.00000000004</v>
       </c>
       <c r="D19">
-        <v>71.98424295248098</v>
+        <v>69.70204471504753</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -787,13 +787,13 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>-7749.495693290531</v>
+        <v>-7697.000379938183</v>
       </c>
       <c r="C20">
         <v>-25108.00000000009</v>
       </c>
       <c r="D20">
-        <v>69.13535250402062</v>
+        <v>69.34443054031323</v>
       </c>
       <c r="E20">
         <v>300</v>
@@ -807,13 +807,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-12950.00061152834</v>
+        <v>-12735.99222286741</v>
       </c>
       <c r="C21">
         <v>-28000</v>
       </c>
       <c r="D21">
-        <v>53.74999781597022</v>
+        <v>54.51431348975924</v>
       </c>
       <c r="E21">
         <v>300</v>
@@ -897,16 +897,16 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>-145.000010023737</v>
+        <v>-145.0000103262423</v>
       </c>
       <c r="C4">
-        <v>-145.000010023737</v>
+        <v>-145.0000103262423</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -917,16 +917,16 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-451.0000206246843</v>
+        <v>-451.0000189340461</v>
       </c>
       <c r="C5">
-        <v>-451.0000206246843</v>
+        <v>-451.0000189340461</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -937,13 +937,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-565.0000159276717</v>
+        <v>-565.0000166768514</v>
       </c>
       <c r="C6">
         <v>-1771.731492813431</v>
       </c>
       <c r="D6">
-        <v>68.11029107856085</v>
+        <v>68.11029103627568</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -957,13 +957,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-728.0000202896014</v>
+        <v>-728.0000098991554</v>
       </c>
       <c r="C7">
         <v>-3426.505201707036</v>
       </c>
       <c r="D7">
-        <v>78.75386210045961</v>
+        <v>78.75386240369703</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -977,13 +977,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-660.0000183779347</v>
+        <v>-660.0000194420804</v>
       </c>
       <c r="C8">
         <v>-5404.117354618282</v>
       </c>
       <c r="D8">
-        <v>87.78708945293521</v>
+        <v>87.78708943324382</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -997,13 +997,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-698.4933507422611</v>
+        <v>-694.7433525597696</v>
       </c>
       <c r="C9">
         <v>-6136.465232134065</v>
       </c>
       <c r="D9">
-        <v>88.61733385069066</v>
+        <v>88.67844392042355</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1017,13 +1017,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-742.7498734940593</v>
+        <v>-742.7498706023927</v>
       </c>
       <c r="C10">
         <v>-7391.707267549545</v>
       </c>
       <c r="D10">
-        <v>89.95157888956429</v>
+        <v>89.95157892868471</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1077,13 +1077,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-1108.000047195343</v>
+        <v>-1108.000046335271</v>
       </c>
       <c r="C13">
         <v>-10770.96185463446</v>
       </c>
       <c r="D13">
-        <v>89.71308168992725</v>
+        <v>89.71308169791237</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1737,13 +1737,13 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>-86.00000000000003</v>
+        <v>-86</v>
       </c>
       <c r="C3">
         <v>-86.00000000000003</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>3.304849933767907E-14</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1777,10 +1777,10 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-451.0000343272736</v>
+        <v>-451.0000336549871</v>
       </c>
       <c r="C5">
-        <v>-451.0000343272736</v>
+        <v>-451.0000336549871</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1797,16 +1797,16 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-659.0000237442974</v>
+        <v>-659.0000310687153</v>
       </c>
       <c r="C6">
-        <v>-659.0000251974584</v>
+        <v>-659.0000310687153</v>
       </c>
       <c r="D6">
-        <v>2.205100010114148E-07</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -1817,16 +1817,16 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-868.0000571720884</v>
+        <v>-868.000054508189</v>
       </c>
       <c r="C7">
-        <v>-868.0000571720884</v>
+        <v>-868.000054508189</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -1837,13 +1837,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1060.50006049484</v>
+        <v>-1060.500060948525</v>
       </c>
       <c r="C8">
         <v>-1772.544375686975</v>
       </c>
       <c r="D8">
-        <v>40.17074691944862</v>
+        <v>40.1707468938535</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1857,13 +1857,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-1254.000081548945</v>
+        <v>-1254.000082953479</v>
       </c>
       <c r="C9">
         <v>-2363.082998326638</v>
       </c>
       <c r="D9">
-        <v>46.93372672746003</v>
+        <v>46.9337266680235</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1877,13 +1877,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-1449.000091779117</v>
+        <v>-1449.000096220359</v>
       </c>
       <c r="C10">
-        <v>-2845.549047076071</v>
+        <v>-2843.70612244898</v>
       </c>
       <c r="D10">
-        <v>49.07836527126356</v>
+        <v>49.0453642596342</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -1897,13 +1897,13 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-1635.000163509643</v>
+        <v>-1635.000159575377</v>
       </c>
       <c r="C11">
         <v>-3318.756098918216</v>
       </c>
       <c r="D11">
-        <v>50.73454888587358</v>
+        <v>50.73454900441997</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -1917,13 +1917,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-1997.625110585045</v>
+        <v>-1998.750134015417</v>
       </c>
       <c r="C12">
         <v>-4244.750460012079</v>
       </c>
       <c r="D12">
-        <v>52.93892704874433</v>
+        <v>52.91242317199184</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -1937,13 +1937,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-2173.000155713786</v>
+        <v>-2177.000107557963</v>
       </c>
       <c r="C13">
         <v>-4732.462068965503</v>
       </c>
       <c r="D13">
-        <v>54.08309408407377</v>
+        <v>53.99857250131438</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -1957,13 +1957,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-2538.500231431382</v>
+        <v>-2516.500136313382</v>
       </c>
       <c r="C14">
         <v>-5944.883997635979</v>
       </c>
       <c r="D14">
-        <v>57.29941522087171</v>
+        <v>57.66948291482079</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -1977,13 +1977,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-2918.000230485854</v>
+        <v>-2887.500101202053</v>
       </c>
       <c r="C15">
         <v>-12072.00941456705</v>
       </c>
       <c r="D15">
-        <v>75.82838009582099</v>
+        <v>76.08103173181952</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -1997,13 +1997,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-0.0002131862964693827</v>
+        <v>-0.0002132330841519559</v>
       </c>
       <c r="C16">
         <v>-14700.01230382703</v>
       </c>
       <c r="D16">
-        <v>99.9999985497543</v>
+        <v>99.99999854943601</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -2017,13 +2017,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-4169.000319999496</v>
+        <v>-4156.000323196965</v>
       </c>
       <c r="C17">
         <v>-18203.988754082</v>
       </c>
       <c r="D17">
-        <v>77.09842399751727</v>
+        <v>77.16983690036044</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -2057,13 +2057,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-0.0004529591657500301</v>
+        <v>-0.0004529792364759417</v>
       </c>
       <c r="C19">
         <v>-22054.0168671837</v>
       </c>
       <c r="D19">
-        <v>99.99999794613758</v>
+        <v>99.99999794604658</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -2097,13 +2097,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-0.001315768683549798</v>
+        <v>-0.001315578092946071</v>
       </c>
       <c r="C21">
         <v>-28000</v>
       </c>
       <c r="D21">
-        <v>99.99999530082613</v>
+        <v>99.9999953015068</v>
       </c>
       <c r="E21">
         <v>300</v>
@@ -2187,13 +2187,13 @@
         <v>40</v>
       </c>
       <c r="B4">
-        <v>-145.0000104378069</v>
+        <v>-145.0000109769709</v>
       </c>
       <c r="C4">
         <v>-281.999926757077</v>
       </c>
       <c r="D4">
-        <v>48.58154322759305</v>
+        <v>48.58154303640011</v>
       </c>
       <c r="E4">
         <v>300</v>
@@ -2207,13 +2207,13 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>-195.0000231381525</v>
+        <v>-195.0000231551394</v>
       </c>
       <c r="C5">
         <v>-936.0000000000003</v>
       </c>
       <c r="D5">
-        <v>79.16666419464184</v>
+        <v>79.16666419282699</v>
       </c>
       <c r="E5">
         <v>300</v>
@@ -2227,13 +2227,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>-659.0000335999999</v>
+        <v>-659.0000335998425</v>
       </c>
       <c r="C6">
         <v>-1812.000000000001</v>
       </c>
       <c r="D6">
-        <v>63.63134472406182</v>
+        <v>63.63134472407052</v>
       </c>
       <c r="E6">
         <v>300</v>
@@ -2247,13 +2247,13 @@
         <v>20</v>
       </c>
       <c r="B7">
-        <v>-868.0000555389955</v>
+        <v>-868.0000388794365</v>
       </c>
       <c r="C7">
         <v>-2435.998995109198</v>
       </c>
       <c r="D7">
-        <v>64.36779911314841</v>
+        <v>64.36779979703864</v>
       </c>
       <c r="E7">
         <v>300</v>
@@ -2267,13 +2267,13 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1060.500072872644</v>
+        <v>-1060.500070053991</v>
       </c>
       <c r="C8">
         <v>-3312.004444742535</v>
       </c>
       <c r="D8">
-        <v>67.98011323456771</v>
+        <v>67.98011331967186</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -2287,13 +2287,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-1254.000079633853</v>
+        <v>-1229.500063087243</v>
       </c>
       <c r="C9">
         <v>-4188.005371744407</v>
       </c>
       <c r="D9">
-        <v>70.05734309477424</v>
+        <v>70.64234751506237</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -2307,13 +2307,13 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>-1442.0000948294</v>
+        <v>-1429.000046700349</v>
       </c>
       <c r="C10">
         <v>-5064.000362915775</v>
       </c>
       <c r="D10">
-        <v>71.52448673998281</v>
+        <v>71.78120173203241</v>
       </c>
       <c r="E10">
         <v>300</v>
@@ -2327,13 +2327,13 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>-1616.000115152116</v>
+        <v>-1635.000172391572</v>
       </c>
       <c r="C11">
         <v>-5939.994871392595</v>
       </c>
       <c r="D11">
-        <v>72.79458736681947</v>
+        <v>72.47472080715355</v>
       </c>
       <c r="E11">
         <v>300</v>
@@ -2347,13 +2347,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>-1997.000146613521</v>
+        <v>-2002.000102352629</v>
       </c>
       <c r="C12">
         <v>-7691.994480834661</v>
       </c>
       <c r="D12">
-        <v>74.03794098410707</v>
+        <v>73.97293891277738</v>
       </c>
       <c r="E12">
         <v>300</v>
@@ -2367,13 +2367,13 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <v>-2194.500111271641</v>
+        <v>-2193.000100743322</v>
       </c>
       <c r="C13">
         <v>-8567.994145187473</v>
       </c>
       <c r="D13">
-        <v>74.38723610117938</v>
+        <v>74.40474323882327</v>
       </c>
       <c r="E13">
         <v>300</v>
@@ -2387,13 +2387,13 @@
         <v>8</v>
       </c>
       <c r="B14">
-        <v>-2536.500062055725</v>
+        <v>-2544.000195999946</v>
       </c>
       <c r="C14">
         <v>-10319.99875493886</v>
       </c>
       <c r="D14">
-        <v>75.42150806130836</v>
+        <v>75.34883233602659</v>
       </c>
       <c r="E14">
         <v>300</v>
@@ -2407,13 +2407,13 @@
         <v>7</v>
       </c>
       <c r="B15">
-        <v>-2937.500192841713</v>
+        <v>-2937.500196281977</v>
       </c>
       <c r="C15">
         <v>-12072.00941456705</v>
       </c>
       <c r="D15">
-        <v>75.6668497185142</v>
+        <v>75.66684969001636</v>
       </c>
       <c r="E15">
         <v>300</v>
@@ -2427,13 +2427,13 @@
         <v>6</v>
       </c>
       <c r="B16">
-        <v>-3476.437746861758</v>
+        <v>-3493.000242188188</v>
       </c>
       <c r="C16">
         <v>-14700.01230382703</v>
       </c>
       <c r="D16">
-        <v>76.35078342106765</v>
+        <v>76.23811347913761</v>
       </c>
       <c r="E16">
         <v>300</v>
@@ -2447,13 +2447,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>-4234.437719060752</v>
+        <v>-4234.437729240155</v>
       </c>
       <c r="C17">
         <v>-18203.988754082</v>
       </c>
       <c r="D17">
-        <v>76.73895663052836</v>
+        <v>76.73895657460984</v>
       </c>
       <c r="E17">
         <v>300</v>
@@ -2467,13 +2467,13 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>-5014.000299135063</v>
+        <v>-4922.000425596384</v>
       </c>
       <c r="C18">
         <v>-20524.00000000002</v>
       </c>
       <c r="D18">
-        <v>75.57006285745928</v>
+        <v>76.0183179419393</v>
       </c>
       <c r="E18">
         <v>300</v>
@@ -2487,13 +2487,13 @@
         <v>3</v>
       </c>
       <c r="B19">
-        <v>-6392.000456630823</v>
+        <v>-6431.000449959709</v>
       </c>
       <c r="C19">
         <v>-22084.00000000004</v>
       </c>
       <c r="D19">
-        <v>71.05596605401733</v>
+        <v>70.87936764191406</v>
       </c>
       <c r="E19">
         <v>300</v>
@@ -2507,13 +2507,13 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>-7878.001293186947</v>
+        <v>-7878.001288793273</v>
       </c>
       <c r="C20">
         <v>-25108.00000000009</v>
       </c>
       <c r="D20">
-        <v>68.62354112957257</v>
+        <v>68.62354114707168</v>
       </c>
       <c r="E20">
         <v>300</v>
@@ -2527,13 +2527,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>-0.001396066706475298</v>
+        <v>-0.001396267928002813</v>
       </c>
       <c r="C21">
         <v>-28000</v>
       </c>
       <c r="D21">
-        <v>99.99999501404749</v>
+        <v>99.99999501332883</v>
       </c>
       <c r="E21">
         <v>300</v>
